--- a/Outputs/Scenarios/PtX_demand_BE_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BE_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001354470379864105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01693341080084688</v>
+        <v>0.009498761543690178</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.005644470266948961</v>
+        <v>0.01310651285373824</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>1.951562544001469e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005644470266948961</v>
+        <v>0.005617076937316389</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002005128495497259</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09118027495353119</v>
+        <v>0.05114738545340099</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0303934249845104</v>
+        <v>0.07057381762840571</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001055330787103821</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0303934249845104</v>
+        <v>0.03024592184074531</v>
       </c>
     </row>
     <row r="43">
